--- a/data/gravel/Moots MXC 2025.xlsx
+++ b/data/gravel/Moots MXC 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B547A7F-F189-184E-8E19-B3C4DF0D6B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1D66DA-6E76-BF41-995B-37702205D9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25560" yWindow="-17740" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34560" yWindow="-18400" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="99">
   <si>
     <t>brand</t>
   </si>
@@ -323,16 +323,13 @@
     <t>threaded</t>
   </si>
   <si>
-    <t>rider_min_spec</t>
-  </si>
-  <si>
-    <t>rider_max_spec</t>
-  </si>
-  <si>
-    <t>usd</t>
-  </si>
-  <si>
-    <t>a8:f33</t>
+    <t>estimate is 494</t>
+  </si>
+  <si>
+    <t>a8:f31</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -687,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -738,7 +735,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -1054,6 +1051,9 @@
       <c r="F25">
         <v>503</v>
       </c>
+      <c r="G25" s="1" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -1128,20 +1128,16 @@
         <v>31</v>
       </c>
       <c r="C30">
-        <f>C32</f>
         <v>157</v>
       </c>
       <c r="D30">
-        <f>AVERAGE(D32,C33)</f>
-        <v>166.5</v>
+        <v>165</v>
       </c>
       <c r="E30">
-        <f t="shared" ref="E30:F30" si="0">AVERAGE(E32,D33)</f>
-        <v>176.5</v>
+        <v>175</v>
       </c>
       <c r="F30">
-        <f t="shared" si="0"/>
-        <v>186.5</v>
+        <v>185</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1152,313 +1148,278 @@
         <v>32</v>
       </c>
       <c r="C31">
-        <f>D30</f>
-        <v>166.5</v>
+        <v>168</v>
       </c>
       <c r="D31">
-        <f t="shared" ref="D31:E31" si="1">E30</f>
-        <v>176.5</v>
+        <v>178</v>
       </c>
       <c r="E31">
-        <f t="shared" si="1"/>
-        <v>186.5</v>
+        <v>188</v>
       </c>
       <c r="F31">
-        <f>F33</f>
         <v>196</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32">
-        <v>157</v>
-      </c>
-      <c r="D32">
-        <v>165</v>
-      </c>
-      <c r="E32">
-        <v>175</v>
-      </c>
-      <c r="F32">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33">
-        <v>168</v>
-      </c>
-      <c r="D33">
-        <v>178</v>
-      </c>
-      <c r="E33">
-        <v>188</v>
-      </c>
-      <c r="F33">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>70</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
         <v>38</v>
       </c>
-      <c r="B42">
+      <c r="B40">
         <f>2.4*25.4</f>
         <v>60.959999999999994</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48">
-        <v>148</v>
+        <v>46</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B49">
-        <v>110</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>46</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>95</v>
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>30.9</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B52">
-        <v>30.9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>49</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>50</v>
-      </c>
-      <c r="B54">
-        <v>38</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>180</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>53</v>
-      </c>
-      <c r="B57">
-        <v>180</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>55</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B59" s="1"/>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>57</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>59</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>60</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B64" s="1"/>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>62</v>
-      </c>
-      <c r="B66" s="1"/>
+        <v>64</v>
+      </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>63</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>73</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="B67" s="1"/>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>66</v>
+      </c>
+      <c r="B68" s="1">
+        <v>5399</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>65</v>
-      </c>
-      <c r="B69" s="1"/>
+        <v>67</v>
+      </c>
+      <c r="B69">
+        <v>12320</v>
+      </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>66</v>
-      </c>
-      <c r="B70" s="1">
-        <v>5399</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="B70" s="1"/>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>67</v>
-      </c>
-      <c r="B71">
-        <v>12320</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>68</v>
-      </c>
-      <c r="B72" s="1"/>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
         <v>69</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B71" s="1" t="s">
         <v>98</v>
       </c>
     </row>

--- a/data/gravel/Moots MXC 2025.xlsx
+++ b/data/gravel/Moots MXC 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1D66DA-6E76-BF41-995B-37702205D9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2745C08-6EE9-394B-BC55-066A101E8AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34560" yWindow="-18400" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="100">
   <si>
     <t>brand</t>
   </si>
@@ -330,6 +330,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>https://moots.com/wp-content/uploads/2024/05/MXC-Frostbite-01.jpg.webp</t>
   </si>
 </sst>
 </file>
@@ -730,6 +733,11 @@
         <v>89</v>
       </c>
     </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>99</v>
+      </c>
+    </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Moots MXC 2025.xlsx
+++ b/data/gravel/Moots MXC 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2745C08-6EE9-394B-BC55-066A101E8AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40BB136-AFAB-2847-998C-22848D558860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="-18400" windowWidth="25540" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9880" yWindow="960" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="102">
   <si>
     <t>brand</t>
   </si>
@@ -333,6 +333,12 @@
   </si>
   <si>
     <t>https://moots.com/wp-content/uploads/2024/05/MXC-Frostbite-01.jpg.webp</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Steamboat Springs, Colorado, USA</t>
   </si>
 </sst>
 </file>
@@ -687,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1431,6 +1437,14 @@
         <v>98</v>
       </c>
     </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>100</v>
+      </c>
+      <c r="B72" t="s">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Moots MXC 2025.xlsx
+++ b/data/gravel/Moots MXC 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40BB136-AFAB-2847-998C-22848D558860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25555641-B855-A242-94C7-362C4A7715DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9880" yWindow="960" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -339,6 +339,24 @@
   </si>
   <si>
     <t>Steamboat Springs, Colorado, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -693,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1285,163 +1303,193 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>46</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>48</v>
-      </c>
-      <c r="B50">
-        <v>30.9</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>49</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>50</v>
-      </c>
-      <c r="B52">
-        <v>38</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>53</v>
-      </c>
-      <c r="B55">
-        <v>180</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B56">
+        <v>30.9</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>56</v>
+        <v>50</v>
+      </c>
+      <c r="B58">
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>57</v>
-      </c>
-      <c r="B59" s="1"/>
+        <v>51</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>62</v>
-      </c>
-      <c r="B64" s="1"/>
+        <v>56</v>
+      </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>63</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>73</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B65" s="1"/>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>65</v>
-      </c>
-      <c r="B67" s="1"/>
+        <v>59</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
+      </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>66</v>
-      </c>
-      <c r="B68" s="1">
-        <v>5399</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>67</v>
-      </c>
-      <c r="B69">
-        <v>12320</v>
+        <v>61</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B70" s="1"/>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>65</v>
+      </c>
+      <c r="B73" s="1"/>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>66</v>
+      </c>
+      <c r="B74" s="1">
+        <v>5399</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>67</v>
+      </c>
+      <c r="B75">
+        <v>12320</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>68</v>
+      </c>
+      <c r="B76" s="1"/>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>69</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>100</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>101</v>
       </c>
     </row>

--- a/data/gravel/Moots MXC 2025.xlsx
+++ b/data/gravel/Moots MXC 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25555641-B855-A242-94C7-362C4A7715DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F534266D-391D-3942-A21A-EE9E4C9DEAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -332,9 +332,6 @@
     <t>USD</t>
   </si>
   <si>
-    <t>https://moots.com/wp-content/uploads/2024/05/MXC-Frostbite-01.jpg.webp</t>
-  </si>
-  <si>
     <t>location</t>
   </si>
   <si>
@@ -357,6 +354,9 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>https://moots.com/cdn/shop/files/MXCFrostbite01_50253dc5-e144-4ed1-8fd0-f307831fa613.jpg?v=1760652398&amp;width=2200</t>
   </si>
 </sst>
 </file>
@@ -759,7 +759,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -1303,32 +1303,32 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -1487,10 +1487,10 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>99</v>
+      </c>
+      <c r="B78" t="s">
         <v>100</v>
-      </c>
-      <c r="B78" t="s">
-        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Moots MXC 2025.xlsx
+++ b/data/gravel/Moots MXC 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F534266D-391D-3942-A21A-EE9E4C9DEAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77303684-F789-8A4F-9665-CB6DAB47E08D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7400" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -302,9 +302,6 @@
     <t>MXC</t>
   </si>
   <si>
-    <t>https://moots.com/bikes/mountain/mxc/</t>
-  </si>
-  <si>
     <t>fork_travel</t>
   </si>
   <si>
@@ -323,12 +320,6 @@
     <t>threaded</t>
   </si>
   <si>
-    <t>estimate is 494</t>
-  </si>
-  <si>
-    <t>a8:f31</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
@@ -357,6 +348,18 @@
   </si>
   <si>
     <t>https://moots.com/cdn/shop/files/MXCFrostbite01_50253dc5-e144-4ed1-8fd0-f307831fa613.jpg?v=1760652398&amp;width=2200</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:f32</t>
+  </si>
+  <si>
+    <t>https://moots.com/products/mxc-web-devo?srsltid=AfmBOoocgLnMlBOp_viX8kZiLTLdRScaqlAole-5tubxqYtpwN1Tz_Po</t>
+  </si>
+  <si>
+    <t>sid ultimate 100</t>
   </si>
 </sst>
 </file>
@@ -711,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -754,12 +757,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -767,7 +770,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -942,7 +945,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
         <v>79</v>
@@ -1026,191 +1029,189 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="C20">
+        <v>44</v>
+      </c>
+      <c r="D20">
+        <v>44</v>
+      </c>
+      <c r="E20">
+        <v>44</v>
+      </c>
+      <c r="F20">
+        <v>44</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C21">
-        <v>44</v>
+        <v>506</v>
       </c>
       <c r="D21">
-        <v>44</v>
+        <v>506</v>
       </c>
       <c r="E21">
-        <v>44</v>
+        <v>506</v>
       </c>
       <c r="F21">
-        <v>44</v>
+        <v>506</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
+      <c r="A22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G22" s="4"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>24</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25">
-        <v>503</v>
-      </c>
-      <c r="D25">
-        <v>503</v>
-      </c>
-      <c r="E25">
-        <v>503</v>
-      </c>
-      <c r="F25">
-        <v>503</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27">
-        <v>29</v>
-      </c>
-      <c r="D27">
-        <v>29</v>
-      </c>
-      <c r="E27">
-        <v>29</v>
-      </c>
-      <c r="F27">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28">
         <v>29</v>
       </c>
-      <c r="B28" t="s">
+      <c r="D28">
         <v>29</v>
       </c>
-      <c r="C28">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="D28">
-        <v>2.2000000000000002</v>
-      </c>
       <c r="E28">
-        <v>2.2000000000000002</v>
+        <v>29</v>
       </c>
       <c r="F28">
-        <v>2.2000000000000002</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="D29">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E29">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F29">
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30">
-        <v>157</v>
+        <v>2.4</v>
       </c>
       <c r="D30">
-        <v>165</v>
+        <v>2.4</v>
       </c>
       <c r="E30">
-        <v>175</v>
+        <v>2.4</v>
       </c>
       <c r="F30">
-        <v>185</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31">
+        <v>157</v>
+      </c>
+      <c r="D31">
+        <v>165</v>
+      </c>
+      <c r="E31">
+        <v>175</v>
+      </c>
+      <c r="F31">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" t="s">
         <v>32</v>
       </c>
-      <c r="C31">
+      <c r="C32">
         <v>168</v>
       </c>
-      <c r="D31">
+      <c r="D32">
         <v>178</v>
       </c>
-      <c r="E31">
+      <c r="E32">
         <v>188</v>
       </c>
-      <c r="F31">
+      <c r="F32">
         <v>196</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>70</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>94</v>
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>93</v>
@@ -1218,58 +1219,58 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>38</v>
       </c>
-      <c r="B40">
+      <c r="B41">
         <f>2.4*25.4</f>
         <v>60.959999999999994</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>39</v>
-      </c>
-    </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42">
-        <v>100</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43">
         <v>100</v>
@@ -1277,220 +1278,228 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>42</v>
+        <v>41</v>
+      </c>
+      <c r="B44">
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46">
-        <v>148</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B47">
-        <v>110</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>101</v>
+        <v>45</v>
+      </c>
+      <c r="B48">
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>46</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>48</v>
-      </c>
-      <c r="B56">
-        <v>30.9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>49</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>74</v>
+        <v>48</v>
+      </c>
+      <c r="B57">
+        <v>30.9</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>50</v>
-      </c>
-      <c r="B58">
-        <v>38</v>
+        <v>49</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="B59">
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>53</v>
-      </c>
-      <c r="B61">
-        <v>180</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="B62">
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>57</v>
-      </c>
-      <c r="B65" s="1"/>
+        <v>56</v>
+      </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>58</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>62</v>
-      </c>
-      <c r="B70" s="1"/>
+        <v>61</v>
+      </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>63</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>73</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B71" s="1"/>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>64</v>
+        <v>63</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>65</v>
-      </c>
-      <c r="B73" s="1"/>
+        <v>64</v>
+      </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>66</v>
-      </c>
-      <c r="B74" s="1">
-        <v>5399</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="B74" s="1"/>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>67</v>
-      </c>
-      <c r="B75">
-        <v>12320</v>
+        <v>66</v>
+      </c>
+      <c r="B75" s="1">
+        <v>5399</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>68</v>
-      </c>
-      <c r="B76" s="1"/>
+        <v>67</v>
+      </c>
+      <c r="B76">
+        <v>12320</v>
+      </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>69</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>98</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="B77" s="1"/>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>99</v>
-      </c>
-      <c r="B78" t="s">
-        <v>100</v>
+        <v>69</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>96</v>
+      </c>
+      <c r="B79" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
